--- a/artfynd/A 21993-2025 artfynd.xlsx
+++ b/artfynd/A 21993-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1698,6 +1698,1138 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125575326</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Karhulompolo, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>880292</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7397645</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Födosök på gran</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125575335</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56828</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Karhulompolo, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>880297</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7397740</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125575328</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80057</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Karhulompolo, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>880273</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7397667</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125575344</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Karhulompolo, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>880506</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7397440</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125575336</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91750</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1179</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gräddticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Perenniporia subacida</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Peck) Donk</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Karhulompolo, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>880311</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7397716</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125575331</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Karhulompolo, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>880249</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7397641</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125575337</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91184</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Karhulompolo, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>880395</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7397707</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125575343</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Karhulompolo, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>880194</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7397559</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125575327</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80057</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Karhulompolo, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>880249</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7397641</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125575330</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80057</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Karhulompolo, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>880225</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7397487</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125575334</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Karhulompolo, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>880192</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7397532</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21993-2025 artfynd.xlsx
+++ b/artfynd/A 21993-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125547267</v>
+        <v>125547270</v>
       </c>
       <c r="B2" t="n">
-        <v>98290</v>
+        <v>57632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>880437</v>
+        <v>880489</v>
       </c>
       <c r="R2" t="n">
-        <v>7397629</v>
+        <v>7397481</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125547270</v>
+        <v>125547263</v>
       </c>
       <c r="B3" t="n">
-        <v>57632</v>
+        <v>58111</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>880489</v>
+        <v>880309</v>
       </c>
       <c r="R3" t="n">
-        <v>7397481</v>
+        <v>7397717</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125547263</v>
+        <v>125547269</v>
       </c>
       <c r="B5" t="n">
-        <v>58111</v>
+        <v>57632</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>880309</v>
+        <v>880372</v>
       </c>
       <c r="R5" t="n">
-        <v>7397717</v>
+        <v>7397490</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125547268</v>
+        <v>125547274</v>
       </c>
       <c r="B6" t="n">
-        <v>57632</v>
+        <v>98269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>880411</v>
+        <v>880198</v>
       </c>
       <c r="R6" t="n">
-        <v>7397678</v>
+        <v>7397502</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1159,11 +1159,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125547269</v>
+        <v>125547265</v>
       </c>
       <c r="B7" t="n">
-        <v>57632</v>
+        <v>80057</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>880372</v>
+        <v>880295</v>
       </c>
       <c r="R7" t="n">
-        <v>7397490</v>
+        <v>7397683</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1394,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125547264</v>
+        <v>125547267</v>
       </c>
       <c r="B9" t="n">
-        <v>80057</v>
+        <v>98290</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>880398</v>
+        <v>880437</v>
       </c>
       <c r="R9" t="n">
-        <v>7397722</v>
+        <v>7397629</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125547274</v>
+        <v>125547264</v>
       </c>
       <c r="B10" t="n">
-        <v>98269</v>
+        <v>80057</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>880198</v>
+        <v>880398</v>
       </c>
       <c r="R10" t="n">
-        <v>7397502</v>
+        <v>7397722</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125547265</v>
+        <v>125547268</v>
       </c>
       <c r="B11" t="n">
-        <v>80057</v>
+        <v>57632</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>880295</v>
+        <v>880411</v>
       </c>
       <c r="R11" t="n">
-        <v>7397683</v>
+        <v>7397678</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1674,6 +1669,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125575326</v>
+        <v>125575337</v>
       </c>
       <c r="B12" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>880292</v>
+        <v>880395</v>
       </c>
       <c r="R12" t="n">
-        <v>7397645</v>
+        <v>7397707</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1776,11 +1776,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Födosök på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125575335</v>
+        <v>125575327</v>
       </c>
       <c r="B13" t="n">
-        <v>56828</v>
+        <v>80057</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>880297</v>
+        <v>880249</v>
       </c>
       <c r="R13" t="n">
-        <v>7397740</v>
+        <v>7397641</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1883,11 +1878,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,7 +1904,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125575328</v>
+        <v>125575330</v>
       </c>
       <c r="B14" t="n">
         <v>80057</v>
@@ -1954,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>880273</v>
+        <v>880225</v>
       </c>
       <c r="R14" t="n">
-        <v>7397667</v>
+        <v>7397487</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2016,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125575344</v>
+        <v>125575328</v>
       </c>
       <c r="B15" t="n">
-        <v>78947</v>
+        <v>80057</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,25 +2018,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>880506</v>
+        <v>880273</v>
       </c>
       <c r="R15" t="n">
-        <v>7397440</v>
+        <v>7397667</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2118,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125575336</v>
+        <v>125575331</v>
       </c>
       <c r="B16" t="n">
-        <v>91750</v>
+        <v>80028</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1179</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>880311</v>
+        <v>880249</v>
       </c>
       <c r="R16" t="n">
-        <v>7397716</v>
+        <v>7397641</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2220,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125575331</v>
+        <v>125575344</v>
       </c>
       <c r="B17" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2236,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>880249</v>
+        <v>880506</v>
       </c>
       <c r="R17" t="n">
-        <v>7397641</v>
+        <v>7397440</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2322,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125575337</v>
+        <v>125575326</v>
       </c>
       <c r="B18" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2362,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>880395</v>
+        <v>880292</v>
       </c>
       <c r="R18" t="n">
-        <v>7397707</v>
+        <v>7397645</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2398,6 +2388,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Födosök på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2424,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125575343</v>
+        <v>125575336</v>
       </c>
       <c r="B19" t="n">
-        <v>78947</v>
+        <v>91750</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2436,25 +2431,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1179</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>880194</v>
+        <v>880311</v>
       </c>
       <c r="R19" t="n">
-        <v>7397559</v>
+        <v>7397716</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2526,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125575327</v>
+        <v>125575334</v>
       </c>
       <c r="B20" t="n">
-        <v>80057</v>
+        <v>98269</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2538,25 +2533,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>880249</v>
+        <v>880192</v>
       </c>
       <c r="R20" t="n">
-        <v>7397641</v>
+        <v>7397532</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2628,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125575330</v>
+        <v>125575343</v>
       </c>
       <c r="B21" t="n">
-        <v>80057</v>
+        <v>78947</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2640,25 +2635,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>880225</v>
+        <v>880194</v>
       </c>
       <c r="R21" t="n">
-        <v>7397487</v>
+        <v>7397559</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2730,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125575334</v>
+        <v>125575335</v>
       </c>
       <c r="B22" t="n">
-        <v>98269</v>
+        <v>56828</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2742,25 +2737,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2770,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>880192</v>
+        <v>880297</v>
       </c>
       <c r="R22" t="n">
-        <v>7397532</v>
+        <v>7397740</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2806,6 +2801,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 21993-2025 artfynd.xlsx
+++ b/artfynd/A 21993-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125547263</v>
+        <v>125547273</v>
       </c>
       <c r="B3" t="n">
-        <v>58111</v>
+        <v>98269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103018</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>880309</v>
+        <v>880267</v>
       </c>
       <c r="R3" t="n">
-        <v>7397717</v>
+        <v>7397620</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125547273</v>
+        <v>125547263</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
+        <v>58111</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>880267</v>
+        <v>880309</v>
       </c>
       <c r="R4" t="n">
-        <v>7397620</v>
+        <v>7397717</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 21993-2025 artfynd.xlsx
+++ b/artfynd/A 21993-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125547270</v>
+        <v>125547274</v>
       </c>
       <c r="B2" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>880489</v>
+        <v>880198</v>
       </c>
       <c r="R2" t="n">
-        <v>7397481</v>
+        <v>7397502</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125547273</v>
+        <v>125547268</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>880267</v>
+        <v>880411</v>
       </c>
       <c r="R3" t="n">
-        <v>7397620</v>
+        <v>7397678</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -853,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,37 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125547263</v>
+        <v>125547265</v>
       </c>
       <c r="B4" t="n">
-        <v>58111</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103018</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>880309</v>
+        <v>880295</v>
       </c>
       <c r="R4" t="n">
-        <v>7397717</v>
+        <v>7397683</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,15 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125547269</v>
+        <v>125547270</v>
       </c>
       <c r="B5" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>880372</v>
+        <v>880489</v>
       </c>
       <c r="R5" t="n">
-        <v>7397490</v>
+        <v>7397481</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,37 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125547274</v>
+        <v>125547266</v>
       </c>
       <c r="B6" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>880198</v>
+        <v>880208</v>
       </c>
       <c r="R6" t="n">
-        <v>7397502</v>
+        <v>7397578</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,37 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125547265</v>
+        <v>125547269</v>
       </c>
       <c r="B7" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>880295</v>
+        <v>880372</v>
       </c>
       <c r="R7" t="n">
-        <v>7397683</v>
+        <v>7397490</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,15 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125547266</v>
+        <v>125547264</v>
       </c>
       <c r="B8" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>880208</v>
+        <v>880398</v>
       </c>
       <c r="R8" t="n">
-        <v>7397578</v>
+        <v>7397722</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1392,12 +1362,7 @@
         <v>125547267</v>
       </c>
       <c r="B9" t="n">
-        <v>98290</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,37 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125547264</v>
+        <v>125547263</v>
       </c>
       <c r="B10" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>103018</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>880398</v>
+        <v>880309</v>
       </c>
       <c r="R10" t="n">
-        <v>7397722</v>
+        <v>7397717</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,37 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125547268</v>
+        <v>125547273</v>
       </c>
       <c r="B11" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>880411</v>
+        <v>880267</v>
       </c>
       <c r="R11" t="n">
-        <v>7397678</v>
+        <v>7397620</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1669,11 +1624,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,37 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125575337</v>
+        <v>125575328</v>
       </c>
       <c r="B12" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>880395</v>
+        <v>880273</v>
       </c>
       <c r="R12" t="n">
-        <v>7397707</v>
+        <v>7397667</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1802,37 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125575327</v>
+        <v>125575331</v>
       </c>
       <c r="B13" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,12 +1847,7 @@
         <v>125575330</v>
       </c>
       <c r="B14" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2006,37 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125575328</v>
+        <v>125575337</v>
       </c>
       <c r="B15" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91238</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>880273</v>
+        <v>880395</v>
       </c>
       <c r="R15" t="n">
-        <v>7397667</v>
+        <v>7397707</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2108,15 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125575331</v>
+        <v>125575335</v>
       </c>
       <c r="B16" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56834</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2124,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>880249</v>
+        <v>880297</v>
       </c>
       <c r="R16" t="n">
-        <v>7397641</v>
+        <v>7397740</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2184,6 +2109,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2210,37 +2140,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125575344</v>
+        <v>125575327</v>
       </c>
       <c r="B17" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>880506</v>
+        <v>880249</v>
       </c>
       <c r="R17" t="n">
-        <v>7397440</v>
+        <v>7397641</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2312,15 +2237,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125575326</v>
+        <v>125575343</v>
       </c>
       <c r="B18" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,21 +2248,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>880292</v>
+        <v>880194</v>
       </c>
       <c r="R18" t="n">
-        <v>7397645</v>
+        <v>7397559</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2388,11 +2308,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Födosök på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2419,37 +2334,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125575336</v>
+        <v>125575326</v>
       </c>
       <c r="B19" t="n">
-        <v>91750</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1179</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>880311</v>
+        <v>880292</v>
       </c>
       <c r="R19" t="n">
-        <v>7397716</v>
+        <v>7397645</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2495,6 +2405,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Födosök på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2521,37 +2436,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125575334</v>
+        <v>125575344</v>
       </c>
       <c r="B20" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>880192</v>
+        <v>880506</v>
       </c>
       <c r="R20" t="n">
-        <v>7397532</v>
+        <v>7397440</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2623,37 +2533,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125575343</v>
+        <v>125575336</v>
       </c>
       <c r="B21" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91804</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1179</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2568,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>880194</v>
+        <v>880311</v>
       </c>
       <c r="R21" t="n">
-        <v>7397559</v>
+        <v>7397716</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2725,37 +2630,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125575335</v>
+        <v>125575334</v>
       </c>
       <c r="B22" t="n">
-        <v>56828</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>880297</v>
+        <v>880192</v>
       </c>
       <c r="R22" t="n">
-        <v>7397740</v>
+        <v>7397532</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2801,11 +2701,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 21993-2025 artfynd.xlsx
+++ b/artfynd/A 21993-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125547274</v>
       </c>
       <c r="B2" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>125547267</v>
       </c>
       <c r="B9" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125547263</v>
+        <v>125547273</v>
       </c>
       <c r="B10" t="n">
-        <v>58129</v>
+        <v>98331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103018</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>880309</v>
+        <v>880267</v>
       </c>
       <c r="R10" t="n">
-        <v>7397717</v>
+        <v>7397620</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1553,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125547273</v>
+        <v>125547263</v>
       </c>
       <c r="B11" t="n">
-        <v>98324</v>
+        <v>58129</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103018</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>880267</v>
+        <v>880309</v>
       </c>
       <c r="R11" t="n">
-        <v>7397620</v>
+        <v>7397717</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1944,7 +1944,7 @@
         <v>125575337</v>
       </c>
       <c r="B15" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>125575336</v>
       </c>
       <c r="B21" t="n">
-        <v>91804</v>
+        <v>91811</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>125575334</v>
       </c>
       <c r="B22" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 21993-2025 artfynd.xlsx
+++ b/artfynd/A 21993-2025 artfynd.xlsx
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125547273</v>
+        <v>125547263</v>
       </c>
       <c r="B10" t="n">
-        <v>98331</v>
+        <v>58129</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103018</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>880267</v>
+        <v>880309</v>
       </c>
       <c r="R10" t="n">
-        <v>7397620</v>
+        <v>7397717</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1553,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125547263</v>
+        <v>125547273</v>
       </c>
       <c r="B11" t="n">
-        <v>58129</v>
+        <v>98331</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103018</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>880309</v>
+        <v>880267</v>
       </c>
       <c r="R11" t="n">
-        <v>7397717</v>
+        <v>7397620</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 21993-2025 artfynd.xlsx
+++ b/artfynd/A 21993-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125547274</v>
       </c>
       <c r="B2" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125547265</v>
       </c>
       <c r="B4" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125547266</v>
       </c>
       <c r="B6" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>125547264</v>
       </c>
       <c r="B8" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>125547267</v>
       </c>
       <c r="B9" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125547263</v>
+        <v>125547273</v>
       </c>
       <c r="B10" t="n">
-        <v>58129</v>
+        <v>98334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103018</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>880309</v>
+        <v>880267</v>
       </c>
       <c r="R10" t="n">
-        <v>7397717</v>
+        <v>7397620</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1553,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125547273</v>
+        <v>125547263</v>
       </c>
       <c r="B11" t="n">
-        <v>98331</v>
+        <v>58130</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103018</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>880267</v>
+        <v>880309</v>
       </c>
       <c r="R11" t="n">
-        <v>7397620</v>
+        <v>7397717</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1653,7 +1653,7 @@
         <v>125575328</v>
       </c>
       <c r="B12" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>125575331</v>
       </c>
       <c r="B13" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>125575330</v>
       </c>
       <c r="B14" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>125575337</v>
       </c>
       <c r="B15" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>125575327</v>
       </c>
       <c r="B17" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>125575343</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>125575344</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>125575336</v>
       </c>
       <c r="B21" t="n">
-        <v>91811</v>
+        <v>91815</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>125575334</v>
       </c>
       <c r="B22" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 21993-2025 artfynd.xlsx
+++ b/artfynd/A 21993-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125547274</v>
       </c>
       <c r="B2" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125547265</v>
       </c>
       <c r="B4" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125547266</v>
       </c>
       <c r="B6" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>125547264</v>
       </c>
       <c r="B8" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>125547267</v>
       </c>
       <c r="B9" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125547273</v>
+        <v>125547263</v>
       </c>
       <c r="B10" t="n">
-        <v>98334</v>
+        <v>58130</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103018</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>880267</v>
+        <v>880309</v>
       </c>
       <c r="R10" t="n">
-        <v>7397620</v>
+        <v>7397717</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1553,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125547263</v>
+        <v>125547273</v>
       </c>
       <c r="B11" t="n">
-        <v>58130</v>
+        <v>98338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103018</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>880309</v>
+        <v>880267</v>
       </c>
       <c r="R11" t="n">
-        <v>7397717</v>
+        <v>7397620</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1653,7 +1653,7 @@
         <v>125575328</v>
       </c>
       <c r="B12" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>125575331</v>
       </c>
       <c r="B13" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>125575330</v>
       </c>
       <c r="B14" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>125575337</v>
       </c>
       <c r="B15" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>125575327</v>
       </c>
       <c r="B17" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125575343</v>
+        <v>125575326</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2248,21 +2248,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>880194</v>
+        <v>880292</v>
       </c>
       <c r="R18" t="n">
-        <v>7397559</v>
+        <v>7397645</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2308,6 +2308,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Födosök på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2334,10 +2339,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125575326</v>
+        <v>125575343</v>
       </c>
       <c r="B19" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2345,21 +2350,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2369,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>880292</v>
+        <v>880194</v>
       </c>
       <c r="R19" t="n">
-        <v>7397645</v>
+        <v>7397559</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2405,11 +2410,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Födosök på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2439,7 +2439,7 @@
         <v>125575344</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>125575336</v>
       </c>
       <c r="B21" t="n">
-        <v>91815</v>
+        <v>91819</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>125575334</v>
       </c>
       <c r="B22" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 21993-2025 artfynd.xlsx
+++ b/artfynd/A 21993-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125547274</v>
       </c>
       <c r="B2" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>125547267</v>
       </c>
       <c r="B9" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>125547273</v>
       </c>
       <c r="B11" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125575326</v>
+        <v>125575343</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2248,21 +2248,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>880292</v>
+        <v>880194</v>
       </c>
       <c r="R18" t="n">
-        <v>7397645</v>
+        <v>7397559</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2308,11 +2308,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Födosök på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2339,10 +2334,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125575343</v>
+        <v>125575326</v>
       </c>
       <c r="B19" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2350,21 +2345,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>880194</v>
+        <v>880292</v>
       </c>
       <c r="R19" t="n">
-        <v>7397559</v>
+        <v>7397645</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2410,6 +2405,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Födosök på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2633,7 +2633,7 @@
         <v>125575334</v>
       </c>
       <c r="B22" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 21993-2025 artfynd.xlsx
+++ b/artfynd/A 21993-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125547274</v>
       </c>
       <c r="B2" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125547268</v>
       </c>
       <c r="B3" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125547265</v>
       </c>
       <c r="B4" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>125547270</v>
       </c>
       <c r="B5" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125547266</v>
       </c>
       <c r="B6" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>125547269</v>
       </c>
       <c r="B7" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>125547264</v>
       </c>
       <c r="B8" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>125547267</v>
       </c>
       <c r="B9" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>125547263</v>
       </c>
       <c r="B10" t="n">
-        <v>58130</v>
+        <v>58131</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>125547273</v>
       </c>
       <c r="B11" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>125575328</v>
       </c>
       <c r="B12" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>125575331</v>
       </c>
       <c r="B13" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>125575330</v>
       </c>
       <c r="B14" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>125575337</v>
       </c>
       <c r="B15" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>125575335</v>
       </c>
       <c r="B16" t="n">
-        <v>56834</v>
+        <v>56835</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>125575327</v>
       </c>
       <c r="B17" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125575343</v>
+        <v>125575326</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>57652</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2248,21 +2248,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>880194</v>
+        <v>880292</v>
       </c>
       <c r="R18" t="n">
-        <v>7397559</v>
+        <v>7397645</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2308,6 +2308,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Födosök på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2334,10 +2339,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125575326</v>
+        <v>125575343</v>
       </c>
       <c r="B19" t="n">
-        <v>57651</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2345,21 +2350,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2369,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>880292</v>
+        <v>880194</v>
       </c>
       <c r="R19" t="n">
-        <v>7397645</v>
+        <v>7397559</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2405,11 +2410,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Födosök på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2439,7 +2439,7 @@
         <v>125575344</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>125575336</v>
       </c>
       <c r="B21" t="n">
-        <v>91819</v>
+        <v>91821</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>125575334</v>
       </c>
       <c r="B22" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 21993-2025 artfynd.xlsx
+++ b/artfynd/A 21993-2025 artfynd.xlsx
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125547263</v>
+        <v>125547273</v>
       </c>
       <c r="B10" t="n">
-        <v>58131</v>
+        <v>98341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103018</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>880309</v>
+        <v>880267</v>
       </c>
       <c r="R10" t="n">
-        <v>7397717</v>
+        <v>7397620</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1553,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125547273</v>
+        <v>125547263</v>
       </c>
       <c r="B11" t="n">
-        <v>98341</v>
+        <v>58131</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103018</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>880267</v>
+        <v>880309</v>
       </c>
       <c r="R11" t="n">
-        <v>7397620</v>
+        <v>7397717</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125575326</v>
+        <v>125575343</v>
       </c>
       <c r="B18" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2248,21 +2248,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>880292</v>
+        <v>880194</v>
       </c>
       <c r="R18" t="n">
-        <v>7397645</v>
+        <v>7397559</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2308,11 +2308,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Födosök på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2339,10 +2334,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125575343</v>
+        <v>125575326</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2350,21 +2345,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>880194</v>
+        <v>880292</v>
       </c>
       <c r="R19" t="n">
-        <v>7397559</v>
+        <v>7397645</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2410,6 +2405,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Födosök på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 21993-2025 artfynd.xlsx
+++ b/artfynd/A 21993-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125547274</v>
       </c>
       <c r="B2" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>125547267</v>
       </c>
       <c r="B9" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125547273</v>
+        <v>125547263</v>
       </c>
       <c r="B10" t="n">
-        <v>98341</v>
+        <v>58131</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103018</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>880267</v>
+        <v>880309</v>
       </c>
       <c r="R10" t="n">
-        <v>7397620</v>
+        <v>7397717</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1553,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125547263</v>
+        <v>125547273</v>
       </c>
       <c r="B11" t="n">
-        <v>58131</v>
+        <v>98343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103018</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>880309</v>
+        <v>880267</v>
       </c>
       <c r="R11" t="n">
-        <v>7397717</v>
+        <v>7397620</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1944,7 +1944,7 @@
         <v>125575337</v>
       </c>
       <c r="B15" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>125575336</v>
       </c>
       <c r="B21" t="n">
-        <v>91821</v>
+        <v>91823</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>125575334</v>
       </c>
       <c r="B22" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 21993-2025 artfynd.xlsx
+++ b/artfynd/A 21993-2025 artfynd.xlsx
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125575331</v>
+        <v>125575330</v>
       </c>
       <c r="B13" t="n">
-        <v>80076</v>
+        <v>80105</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>880249</v>
+        <v>880225</v>
       </c>
       <c r="R13" t="n">
-        <v>7397641</v>
+        <v>7397487</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125575330</v>
+        <v>125575331</v>
       </c>
       <c r="B14" t="n">
-        <v>80105</v>
+        <v>80076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>880225</v>
+        <v>880249</v>
       </c>
       <c r="R14" t="n">
-        <v>7397487</v>
+        <v>7397641</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1944,7 +1944,7 @@
         <v>125575337</v>
       </c>
       <c r="B15" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125575343</v>
+        <v>125575326</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2248,21 +2248,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>880194</v>
+        <v>880292</v>
       </c>
       <c r="R18" t="n">
-        <v>7397559</v>
+        <v>7397645</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2308,6 +2308,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Födosök på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2334,10 +2339,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125575326</v>
+        <v>125575343</v>
       </c>
       <c r="B19" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2345,21 +2350,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2369,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>880292</v>
+        <v>880194</v>
       </c>
       <c r="R19" t="n">
-        <v>7397645</v>
+        <v>7397559</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2405,11 +2410,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Födosök på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2536,7 +2536,7 @@
         <v>125575336</v>
       </c>
       <c r="B21" t="n">
-        <v>91823</v>
+        <v>91825</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>125575334</v>
       </c>
       <c r="B22" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 21993-2025 artfynd.xlsx
+++ b/artfynd/A 21993-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125547274</v>
+        <v>125575336</v>
       </c>
       <c r="B2" t="n">
-        <v>98343</v>
+        <v>92522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1179</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>880198</v>
+        <v>880311</v>
       </c>
       <c r="R2" t="n">
-        <v>7397502</v>
+        <v>7397716</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125547268</v>
+        <v>125575345</v>
       </c>
       <c r="B3" t="n">
-        <v>57649</v>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>880411</v>
+        <v>880414</v>
       </c>
       <c r="R3" t="n">
-        <v>7397678</v>
+        <v>7397733</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -845,11 +845,6 @@
           <t>2025-05-30</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -862,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125547265</v>
+        <v>125575332</v>
       </c>
       <c r="B4" t="n">
-        <v>80105</v>
+        <v>101299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>1365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>880295</v>
+        <v>880456</v>
       </c>
       <c r="R4" t="n">
-        <v>7397683</v>
+        <v>7397612</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,44 +954,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125547270</v>
+        <v>125575340</v>
       </c>
       <c r="B5" t="n">
-        <v>57649</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>880489</v>
+        <v>880334</v>
       </c>
       <c r="R5" t="n">
-        <v>7397481</v>
+        <v>7397779</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1056,44 +1051,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125547266</v>
+        <v>125575343</v>
       </c>
       <c r="B6" t="n">
-        <v>80105</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>880208</v>
+        <v>880194</v>
       </c>
       <c r="R6" t="n">
-        <v>7397578</v>
+        <v>7397559</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1153,44 +1148,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125547269</v>
+        <v>125575344</v>
       </c>
       <c r="B7" t="n">
-        <v>57649</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>880372</v>
+        <v>880506</v>
       </c>
       <c r="R7" t="n">
-        <v>7397490</v>
+        <v>7397440</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1250,44 +1245,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125547264</v>
+        <v>125575331</v>
       </c>
       <c r="B8" t="n">
-        <v>80105</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>880398</v>
+        <v>880249</v>
       </c>
       <c r="R8" t="n">
-        <v>7397722</v>
+        <v>7397641</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1347,22 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125547267</v>
+        <v>125547264</v>
       </c>
       <c r="B9" t="n">
-        <v>98364</v>
+        <v>80461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>880437</v>
+        <v>880398</v>
       </c>
       <c r="R9" t="n">
-        <v>7397629</v>
+        <v>7397722</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1456,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125547263</v>
+        <v>125547265</v>
       </c>
       <c r="B10" t="n">
-        <v>58131</v>
+        <v>80461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103018</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>880309</v>
+        <v>880295</v>
       </c>
       <c r="R10" t="n">
-        <v>7397717</v>
+        <v>7397683</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1553,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125547273</v>
+        <v>125547266</v>
       </c>
       <c r="B11" t="n">
-        <v>98343</v>
+        <v>80461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>880267</v>
+        <v>880208</v>
       </c>
       <c r="R11" t="n">
-        <v>7397620</v>
+        <v>7397578</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1650,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125575328</v>
+        <v>125575327</v>
       </c>
       <c r="B12" t="n">
-        <v>80105</v>
+        <v>80461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1685,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>880273</v>
+        <v>880249</v>
       </c>
       <c r="R12" t="n">
-        <v>7397667</v>
+        <v>7397641</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1747,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125575330</v>
+        <v>125575328</v>
       </c>
       <c r="B13" t="n">
-        <v>80105</v>
+        <v>80461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1782,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>880225</v>
+        <v>880273</v>
       </c>
       <c r="R13" t="n">
-        <v>7397487</v>
+        <v>7397667</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1844,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125575331</v>
+        <v>125575330</v>
       </c>
       <c r="B14" t="n">
-        <v>80076</v>
+        <v>80461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>880249</v>
+        <v>880225</v>
       </c>
       <c r="R14" t="n">
-        <v>7397641</v>
+        <v>7397487</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1941,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125575337</v>
+        <v>125547268</v>
       </c>
       <c r="B15" t="n">
-        <v>91256</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>880395</v>
+        <v>880411</v>
       </c>
       <c r="R15" t="n">
-        <v>7397707</v>
+        <v>7397678</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2014,6 +2009,11 @@
           <t>2025-05-30</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2026,39 +2026,39 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125575335</v>
+        <v>125547269</v>
       </c>
       <c r="B16" t="n">
-        <v>56835</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>880297</v>
+        <v>880372</v>
       </c>
       <c r="R16" t="n">
-        <v>7397740</v>
+        <v>7397490</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2111,11 +2111,6 @@
           <t>2025-05-30</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2128,22 +2123,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125575327</v>
+        <v>125547270</v>
       </c>
       <c r="B17" t="n">
-        <v>80105</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>880249</v>
+        <v>880489</v>
       </c>
       <c r="R17" t="n">
-        <v>7397641</v>
+        <v>7397481</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2225,12 +2220,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2240,7 +2235,7 @@
         <v>125575326</v>
       </c>
       <c r="B18" t="n">
-        <v>57652</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2339,32 +2334,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125575343</v>
+        <v>125575335</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>57132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>880194</v>
+        <v>880297</v>
       </c>
       <c r="R19" t="n">
-        <v>7397559</v>
+        <v>7397740</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2410,6 +2405,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2436,32 +2436,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125575344</v>
+        <v>125547263</v>
       </c>
       <c r="B20" t="n">
-        <v>78973</v>
+        <v>58439</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>103018</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>880506</v>
+        <v>880309</v>
       </c>
       <c r="R20" t="n">
-        <v>7397440</v>
+        <v>7397717</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2521,22 +2521,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125575336</v>
+        <v>125547273</v>
       </c>
       <c r="B21" t="n">
-        <v>91825</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,21 +2544,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1179</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>880311</v>
+        <v>880267</v>
       </c>
       <c r="R21" t="n">
-        <v>7397716</v>
+        <v>7397620</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2618,22 +2618,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125575334</v>
+        <v>125547274</v>
       </c>
       <c r="B22" t="n">
-        <v>98345</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>880192</v>
+        <v>880198</v>
       </c>
       <c r="R22" t="n">
-        <v>7397532</v>
+        <v>7397502</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2715,15 +2715,306 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125575333</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Karhulompolo, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>880365</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7397797</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
           <t>Marie Persson</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
+      <c r="AX23" t="inlineStr">
         <is>
           <t>Marie Persson</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125575334</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Karhulompolo, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>880192</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7397532</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125547267</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Karhulompolo, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>880437</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7397629</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21993-2025 artfynd.xlsx
+++ b/artfynd/A 21993-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125575336</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125575345</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125575332</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125575340</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125575343</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125575344</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125575331</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125547264</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125547265</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125547266</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125575327</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125575328</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125575330</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2035,6 +2105,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125547268</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125547269</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2229,6 +2309,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125547270</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2331,6 +2416,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125575326</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2433,6 +2523,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125575335</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2530,6 +2625,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125547263</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2627,6 +2727,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125547273</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2724,6 +2829,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125547274</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2821,6 +2931,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125575333</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2918,6 +3033,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125575334</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3015,8 +3135,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125547267</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>